--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Family_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Family_by_Sample_name.xlsx
@@ -505,10 +505,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5918082071325</v>
+        <v>37.6083286086558</v>
       </c>
       <c r="D2" t="n">
-        <v>5.59724283853563</v>
+        <v>5.60163716781323</v>
       </c>
     </row>
     <row r="3">
@@ -519,10 +519,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>19.2288487135942</v>
+        <v>19.218471533848</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24433712249579</v>
+        <v>2.2429594916445</v>
       </c>
     </row>
     <row r="4">
@@ -533,10 +533,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>8.83085837103093</v>
+        <v>8.83030019633991</v>
       </c>
       <c r="D4" t="n">
-        <v>1.18874316365223</v>
+        <v>1.18860523810051</v>
       </c>
     </row>
     <row r="5">
@@ -547,10 +547,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.09463516172468</v>
+        <v>8.09618084032267</v>
       </c>
       <c r="D5" t="n">
-        <v>1.77500895016411</v>
+        <v>1.77463760386218</v>
       </c>
     </row>
     <row r="6">
@@ -561,10 +561,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>6.10421054572848</v>
+        <v>6.10113835323846</v>
       </c>
       <c r="D6" t="n">
-        <v>0.294523157391094</v>
+        <v>0.294258916288561</v>
       </c>
     </row>
     <row r="7">
@@ -575,10 +575,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5.68760810180059</v>
+        <v>5.68487064359714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.202215927141487</v>
+        <v>0.202040563636338</v>
       </c>
     </row>
     <row r="8">
@@ -589,10 +589,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.26967222633716</v>
+        <v>4.26749999551657</v>
       </c>
       <c r="D8" t="n">
-        <v>0.136065425139798</v>
+        <v>0.136006692264525</v>
       </c>
     </row>
     <row r="9">
@@ -603,10 +603,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.82594060539674</v>
+        <v>3.8253130345831</v>
       </c>
       <c r="D9" t="n">
-        <v>0.262571455915814</v>
+        <v>0.262482563188048</v>
       </c>
     </row>
     <row r="10">
@@ -617,10 +617,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>1.60491681905068</v>
+        <v>1.60475341957924</v>
       </c>
       <c r="D10" t="n">
-        <v>0.203347398935847</v>
+        <v>0.203320697582051</v>
       </c>
     </row>
     <row r="11">
@@ -631,10 +631,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.60022858826323</v>
+        <v>1.59952430806309</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11371431019001</v>
+        <v>1.11322173383588</v>
       </c>
     </row>
     <row r="12">
@@ -645,10 +645,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.37355874984232</v>
+        <v>1.37632070583837</v>
       </c>
       <c r="D12" t="n">
-        <v>0.608027825036764</v>
+        <v>0.609441380320974</v>
       </c>
     </row>
     <row r="13">
@@ -659,10 +659,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.477247905242917</v>
+        <v>0.477051715520837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0450023147999319</v>
+        <v>0.0449831141801297</v>
       </c>
     </row>
     <row r="14">
@@ -673,7 +673,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.476758293076138</v>
+        <v>0.476429470271012</v>
       </c>
       <c r="D14"/>
     </row>
@@ -685,10 +685,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.200603042094064</v>
+        <v>0.200530274063592</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0277143701674678</v>
+        <v>0.0276870504707831</v>
       </c>
     </row>
     <row r="16">
@@ -699,7 +699,7 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.115689526293467</v>
+        <v>0.115783032995387</v>
       </c>
       <c r="D16"/>
     </row>
@@ -711,10 +711,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.10336839725838</v>
+        <v>0.10349339817975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0254780013641728</v>
+        <v>0.0254968433941032</v>
       </c>
     </row>
     <row r="18">
@@ -725,10 +725,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0959531044181956</v>
+        <v>0.0959849204084664</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0184027177895018</v>
+        <v>0.0184107366986344</v>
       </c>
     </row>
     <row r="19">
@@ -739,10 +739,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0836277009911762</v>
+        <v>0.0836599616266827</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0227641652334727</v>
+        <v>0.0227635062895201</v>
       </c>
     </row>
     <row r="20">
@@ -753,10 +753,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0433672033818553</v>
+        <v>0.0433731723234349</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0104592563889992</v>
+        <v>0.0104501524378753</v>
       </c>
     </row>
     <row r="21">
@@ -767,10 +767,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0371273683230238</v>
+        <v>0.0371173367362967</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00295780682177908</v>
+        <v>0.00296303691235625</v>
       </c>
     </row>
     <row r="22">
@@ -781,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0313025378626997</v>
+        <v>0.0312869414447345</v>
       </c>
       <c r="D22"/>
     </row>
@@ -793,7 +793,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0302541460960583</v>
+        <v>0.03022256435489</v>
       </c>
       <c r="D23"/>
     </row>
@@ -805,10 +805,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.013929077563761</v>
+        <v>0.013918419012933</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00388577358234299</v>
+        <v>0.00388446211042003</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0137048662778633</v>
+        <v>0.0136905600225104</v>
       </c>
       <c r="D25"/>
     </row>
@@ -831,7 +831,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0130089175550854</v>
+        <v>0.0129953377876777</v>
       </c>
       <c r="D26"/>
     </row>
@@ -843,7 +843,7 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0115462983521061</v>
+        <v>0.0115447261229262</v>
       </c>
       <c r="D27"/>
     </row>
@@ -855,10 +855,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0107555358446505</v>
+        <v>0.0107466373932689</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00383713958969168</v>
+        <v>0.00383148718197804</v>
       </c>
     </row>
     <row r="29">
@@ -869,7 +869,7 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00982099833583932</v>
+        <v>0.00983170785250912</v>
       </c>
       <c r="D29"/>
     </row>
@@ -881,7 +881,7 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00838480264662265</v>
+        <v>0.00838381341592277</v>
       </c>
       <c r="D30"/>
     </row>
@@ -893,7 +893,7 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00632532289747537</v>
+        <v>0.00631872001038943</v>
       </c>
       <c r="D31"/>
     </row>
@@ -905,7 +905,7 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00316266144873768</v>
+        <v>0.00315936000519471</v>
       </c>
       <c r="D32"/>
     </row>
@@ -917,7 +917,7 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00177620413836834</v>
+        <v>0.00177629086912041</v>
       </c>
       <c r="D33"/>
     </row>
@@ -954,10 +954,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7972040101877</v>
+        <v>60.0117510250063</v>
       </c>
       <c r="D2" t="n">
-        <v>18.976589310687</v>
+        <v>19.0438950283452</v>
       </c>
     </row>
     <row r="3">
@@ -968,10 +968,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>18.8193844819027</v>
+        <v>18.7552859859298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.376573834997702</v>
+        <v>0.375228900899286</v>
       </c>
     </row>
     <row r="4">
@@ -982,10 +982,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>6.87383972147645</v>
+        <v>6.85280978827221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.194624258010072</v>
+        <v>0.193961992313444</v>
       </c>
     </row>
     <row r="5">
@@ -996,10 +996,10 @@
         <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>5.08412417040453</v>
+        <v>5.06950231319807</v>
       </c>
       <c r="D5" t="n">
-        <v>0.378320464919258</v>
+        <v>0.377113265596081</v>
       </c>
     </row>
     <row r="6">
@@ -1010,10 +1010,10 @@
         <v>38</v>
       </c>
       <c r="C6" t="n">
-        <v>1.93891184712223</v>
+        <v>1.93261553258066</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0663761273090235</v>
+        <v>0.0661212506766528</v>
       </c>
     </row>
     <row r="7">
@@ -1024,10 +1024,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>1.73075091445215</v>
+        <v>1.72381281041984</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0592720139891462</v>
+        <v>0.0588899026502082</v>
       </c>
     </row>
     <row r="8">
@@ -1038,10 +1038,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.08440498494746</v>
+        <v>1.0256963259798</v>
       </c>
       <c r="D8" t="n">
-        <v>0.346796377127552</v>
+        <v>0.326196478513884</v>
       </c>
     </row>
     <row r="9">
@@ -1052,10 +1052,10 @@
         <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>1.01029569541414</v>
+        <v>1.00732325949899</v>
       </c>
       <c r="D9" t="n">
-        <v>0.155699893922854</v>
+        <v>0.15499034216812</v>
       </c>
     </row>
     <row r="10">
@@ -1063,13 +1063,13 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.918635764339107</v>
+        <v>0.910475120792083</v>
       </c>
       <c r="D10" t="n">
-        <v>0.160565559093251</v>
+        <v>0.0830873994578001</v>
       </c>
     </row>
     <row r="11">
@@ -1077,13 +1077,13 @@
         <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0.913238333415153</v>
+        <v>0.888043173298091</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0833513441043682</v>
+        <v>0.15131718509958</v>
       </c>
     </row>
     <row r="12">
@@ -1094,10 +1094,10 @@
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>0.467429336718295</v>
+        <v>0.466221221516168</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0165814334542619</v>
+        <v>0.0165396320360491</v>
       </c>
     </row>
     <row r="13">
@@ -1108,10 +1108,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>0.402296245812782</v>
+        <v>0.401484811843114</v>
       </c>
       <c r="D13" t="n">
-        <v>0.274871069987508</v>
+        <v>0.274321679413749</v>
       </c>
     </row>
     <row r="14">
@@ -1122,10 +1122,10 @@
         <v>28</v>
       </c>
       <c r="C14" t="n">
-        <v>0.388771183154934</v>
+        <v>0.38760316719193</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0425751732072016</v>
+        <v>0.0424549973041662</v>
       </c>
     </row>
     <row r="15">
@@ -1136,10 +1136,10 @@
         <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.238905071421871</v>
+        <v>0.238795680159351</v>
       </c>
       <c r="D15" t="n">
-        <v>0.166646810861579</v>
+        <v>0.166575165597134</v>
       </c>
     </row>
     <row r="16">
@@ -1150,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0.132284452778502</v>
+        <v>0.13250593027904</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0278585800252594</v>
+        <v>0.0279680233633284</v>
       </c>
     </row>
     <row r="17">
@@ -1164,10 +1164,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.108520301484974</v>
+        <v>0.105343591806292</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0146072490474575</v>
+        <v>0.0136460636697803</v>
       </c>
     </row>
     <row r="18">
@@ -1178,10 +1178,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0412645232350904</v>
+        <v>0.0411239945214958</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00249339953905765</v>
+        <v>0.00248507425191541</v>
       </c>
     </row>
     <row r="19">
@@ -1192,10 +1192,10 @@
         <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0151854301157901</v>
+        <v>0.015146783271896</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00296997966832071</v>
+        <v>0.00296250525510009</v>
       </c>
     </row>
     <row r="20">
@@ -1206,7 +1206,7 @@
         <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00743107690211342</v>
+        <v>0.00741230379725906</v>
       </c>
       <c r="D20"/>
     </row>
@@ -1218,10 +1218,10 @@
         <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00676741122361874</v>
+        <v>0.0067439889623678</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00285785858713188</v>
+        <v>0.00284210346859634</v>
       </c>
     </row>
     <row r="22">
@@ -1232,7 +1232,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00613877383033067</v>
+        <v>0.00612320169641204</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1244,7 +1244,7 @@
         <v>35</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1256,7 +1256,7 @@
         <v>41</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1268,7 +1268,7 @@
         <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00387717660683835</v>
+        <v>0.00386730630254106</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1280,7 +1280,7 @@
         <v>42</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0012924367675278</v>
+        <v>0.00128910210084702</v>
       </c>
       <c r="D26"/>
     </row>
@@ -1317,10 +1317,10 @@
         <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -1331,10 +1331,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -1345,10 +1345,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4378584460888</v>
+        <v>12.4382553298214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.428313229449437</v>
+        <v>0.428325745678215</v>
       </c>
     </row>
     <row r="5">
@@ -1359,10 +1359,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -1373,10 +1373,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -1387,10 +1387,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -1401,10 +1401,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -1415,10 +1415,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>3.83589091559257</v>
+        <v>3.83683841548952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0623380318541722</v>
+        <v>0.0623643528173048</v>
       </c>
     </row>
     <row r="10">
@@ -1429,10 +1429,10 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11433185157042</v>
+        <v>3.11454051303145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0384232790596677</v>
+        <v>0.0384252193784699</v>
       </c>
     </row>
     <row r="11">
@@ -1443,10 +1443,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -1457,10 +1457,10 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>1.32056948721848</v>
+        <v>1.32060121834943</v>
       </c>
       <c r="D12" t="n">
-        <v>0.355227968619002</v>
+        <v>0.35523739701465</v>
       </c>
     </row>
     <row r="13">
@@ -1471,10 +1471,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="14">
@@ -1485,10 +1485,10 @@
         <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="15">
@@ -1499,10 +1499,10 @@
         <v>40</v>
       </c>
       <c r="C15" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D15" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="16">
@@ -1513,10 +1513,10 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0.642172015204204</v>
+        <v>0.642169123069737</v>
       </c>
       <c r="D16" t="n">
-        <v>0.165207216080162</v>
+        <v>0.165199823432465</v>
       </c>
     </row>
     <row r="17">
@@ -1527,10 +1527,10 @@
         <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618749698372989</v>
+        <v>0.618964822119536</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0592935207008076</v>
+        <v>0.0593170263818895</v>
       </c>
     </row>
     <row r="18">
@@ -1541,10 +1541,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>0.491137416768517</v>
+        <v>0.491332939185717</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0357046963386505</v>
+        <v>0.0357189445714107</v>
       </c>
     </row>
     <row r="19">
@@ -1555,10 +1555,10 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.357265870418504</v>
+        <v>0.35731527246983</v>
       </c>
       <c r="D19" t="n">
-        <v>0.152724159139168</v>
+        <v>0.152749757190219</v>
       </c>
     </row>
     <row r="20">
@@ -1569,10 +1569,10 @@
         <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>0.296817331957364</v>
+        <v>0.296857210085557</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0534516862568478</v>
+        <v>0.0534584442625477</v>
       </c>
     </row>
     <row r="21">
@@ -1583,10 +1583,10 @@
         <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="D21" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="22">
@@ -1597,7 +1597,7 @@
         <v>44</v>
       </c>
       <c r="C22" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1609,10 +1609,10 @@
         <v>21</v>
       </c>
       <c r="C23" t="n">
-        <v>0.146974458714768</v>
+        <v>0.146966996070451</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0129045399311217</v>
+        <v>0.0129042651403242</v>
       </c>
     </row>
     <row r="24">
@@ -1623,10 +1623,10 @@
         <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="25">
@@ -1637,10 +1637,10 @@
         <v>38</v>
       </c>
       <c r="C25" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="26">
@@ -1651,10 +1651,10 @@
         <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D26" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="27">
@@ -1665,10 +1665,10 @@
         <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="28">
@@ -1679,7 +1679,7 @@
         <v>17</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="D28"/>
     </row>
@@ -1691,10 +1691,10 @@
         <v>31</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0577451720243945</v>
+        <v>0.0577727984075593</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00615561606809399</v>
+        <v>0.00615693902785514</v>
       </c>
     </row>
     <row r="30">
@@ -1705,7 +1705,7 @@
         <v>41</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D30"/>
     </row>
@@ -1717,7 +1717,7 @@
         <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D31"/>
     </row>
@@ -1729,10 +1729,10 @@
         <v>27</v>
       </c>
       <c r="C32" t="n">
-        <v>0.015787218129565</v>
+        <v>0.0157889711102967</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00588204337348365</v>
+        <v>0.00588424684009715</v>
       </c>
     </row>
     <row r="33">
@@ -1743,10 +1743,10 @@
         <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00727727790575996</v>
+        <v>0.00727632488319893</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0014999434261184</v>
+        <v>0.00149874617041298</v>
       </c>
     </row>
     <row r="34">
@@ -1757,7 +1757,7 @@
         <v>26</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1769,7 +1769,7 @@
         <v>45</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="D35"/>
     </row>
@@ -1781,7 +1781,7 @@
         <v>46</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1793,7 +1793,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00119930614215706</v>
+        <v>0.00119886362192086</v>
       </c>
       <c r="D37"/>
     </row>
